--- a/SQExcel.Portal/src/content/docs/ja/docs/images/large-scale/メインDB_見積＋契約_データ修正.xlsx
+++ b/SQExcel.Portal/src/content/docs/ja/docs/images/large-scale/メインDB_見積＋契約_データ修正.xlsx
@@ -209,6 +209,9 @@
     <x:t>処理結果</x:t>
   </x:si>
   <x:si>
+    <x:t>[UPDATE] データ取り込み成功 処理件数：3件</x:t>
+  </x:si>
+  <x:si>
     <x:t>項目名</x:t>
   </x:si>
   <x:si>
@@ -381,9 +384,6 @@
   </x:si>
   <x:si>
     <x:t>*</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELECT TOP (3)</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -410,6 +410,9 @@
       <x:t>"202607100020","202607100021","202607100022"</x:t>
     </x:r>
     <x:phoneticPr fontId="0"/>
+  </x:si>
+  <x:si>
+    <x:t>SELECT TOP (3)</x:t>
   </x:si>
   <x:si>
     <x:t>202607100020</x:t>
@@ -455,9 +458,6 @@
   </x:si>
   <x:si>
     <x:t>4</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">    quotation_id, client_id, site_operator_id, display_start_date, display_end_date,</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -494,6 +494,12 @@
       <x:t>亮</x:t>
     </x:r>
     <x:phoneticPr fontId="0"/>
+  </x:si>
+  <x:si>
+    <x:t>TRUE</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">    quotation_id, client_id, site_operator_id, display_start_date, display_end_date,</x:t>
   </x:si>
   <x:si>
     <x:t>202607100021</x:t>
@@ -730,12 +736,12 @@
     <x:t>契約状態（1=有効,2=完了,9=解約）</x:t>
   </x:si>
   <x:si>
+    <x:t>202607200035</x:t>
+  </x:si>
+  <x:si>
     <x:t>"202607100020","202607100021","202607100022"</x:t>
   </x:si>
   <x:si>
-    <x:t>202607200035</x:t>
-  </x:si>
-  <x:si>
     <x:t>顧客名：リテール横浜ホームデザイン有限会社、ステータス：契約済み、営業担当者：既存顧客支援課・金子 亮</x:t>
   </x:si>
   <x:si>
@@ -787,10 +793,10 @@
     <x:t>円建て金額</x:t>
   </x:si>
   <x:si>
-    <x:t>TRUE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[UPDATE] データ取り込み成功 処理件数：3件</x:t>
+    <x:t>DB種類</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Microsoft SQL Server</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -904,7 +910,7 @@
       <x:diagonal/>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="34">
+  <x:cellStyleXfs count="36">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="0" hidden="0"/>
@@ -1005,8 +1011,14 @@
     <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="0" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="176" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="176" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="66">
+  <x:cellXfs count="68">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <x:alignment vertical="top"/>
@@ -1246,6 +1258,14 @@
     <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="0" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="176" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="176" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1591,7 +1611,8 @@
     <x:col min="1" max="1" width="18.726562" style="1" customWidth="1"/>
     <x:col min="2" max="2" width="23.179688" style="2" customWidth="1"/>
     <x:col min="3" max="4" width="15.269531" style="2" customWidth="1"/>
-    <x:col min="5" max="6" width="14.453125" style="3" customWidth="1"/>
+    <x:col min="5" max="5" width="18.710625" style="3" customWidth="1"/>
+    <x:col min="6" max="6" width="24.710625" style="3" customWidth="1"/>
     <x:col min="7" max="7" width="34.363281" style="2" customWidth="1"/>
     <x:col min="8" max="9" width="16.726562" style="2" customWidth="1"/>
     <x:col min="10" max="10" width="22.542969" style="4" customWidth="1"/>
@@ -1620,8 +1641,12 @@
       <x:c r="D1" s="42" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E1" s="10"/>
-      <x:c r="F1" s="10"/>
+      <x:c r="E1" s="66" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="F1" s="67" t="s">
+        <x:v>151</x:v>
+      </x:c>
       <x:c r="G1" s="11"/>
       <x:c r="H1" s="11"/>
       <x:c r="I1" s="11"/>
@@ -1641,7 +1666,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B2" s="36" t="s">
-        <x:v>149</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C2" s="11"/>
       <x:c r="D2" s="11"/>
@@ -1663,268 +1688,268 @@
     </x:row>
     <x:row r="3" spans="1:23" ht="29" customHeight="1" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <x:c r="A3" s="44" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B3" s="45" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C3" s="46" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D3" s="46" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E3" s="47" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F3" s="47" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G3" s="46" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H3" s="46" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="I3" s="46" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J3" s="48" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K3" s="48" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="L3" s="48" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M3" s="46" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="N3" s="46" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="O3" s="46" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P3" s="49" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="Q3" s="46" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="R3" s="49" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="S3" s="46" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="T3" s="50" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="U3" s="50" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:23" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <x:c r="A4" s="44" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B4" s="45" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C4" s="46" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D4" s="46" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E4" s="51" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F4" s="51" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G4" s="46" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H4" s="46" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="I4" s="46" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="J4" s="52" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="K4" s="52" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="L4" s="52" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="M4" s="46" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="N4" s="46" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="O4" s="46" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="P4" s="53" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="Q4" s="46" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="R4" s="53" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="S4" s="46" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="T4" s="54"/>
       <x:c r="U4" s="54"/>
     </x:row>
     <x:row r="5" spans="1:23" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <x:c r="A5" s="44" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B5" s="45" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C5" s="46" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D5" s="46" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E5" s="47" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F5" s="47" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G5" s="46" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H5" s="46" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="I5" s="46" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="J5" s="48" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="K5" s="48" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="L5" s="48" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="M5" s="46" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="F5" s="47" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="G5" s="46" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="H5" s="46" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="I5" s="46" t="s">
+      <x:c r="N5" s="46" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="J5" s="48" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="K5" s="48" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="L5" s="48" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="M5" s="46" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="N5" s="46" t="s">
-        <x:v>50</x:v>
-      </x:c>
       <x:c r="O5" s="46" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="P5" s="49" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Q5" s="46" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="R5" s="49" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="R5" s="49" t="s">
-        <x:v>54</x:v>
-      </x:c>
       <x:c r="S5" s="46" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="T5" s="54"/>
       <x:c r="U5" s="54"/>
     </x:row>
     <x:row r="6" spans="1:23" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <x:c r="A6" s="41" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B6" s="45" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C6" s="46" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D6" s="46" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E6" s="47" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F6" s="47" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G6" s="46" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H6" s="46" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="I6" s="46" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="J6" s="48" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="K6" s="48" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="L6" s="48" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M6" s="46" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="H6" s="46" t="s">
+      <x:c r="N6" s="46" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="O6" s="46" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="I6" s="46" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="J6" s="48" t="s">
+      <x:c r="P6" s="49" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="Q6" s="46" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="K6" s="48" t="s">
+      <x:c r="R6" s="49" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="S6" s="46" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="L6" s="48" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="M6" s="46" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="N6" s="46" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="O6" s="46" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="P6" s="49" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="Q6" s="46" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="R6" s="49" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="S6" s="46" t="s">
-        <x:v>58</x:v>
       </x:c>
       <x:c r="T6" s="54"/>
       <x:c r="U6" s="54"/>
     </x:row>
     <x:row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <x:c r="A7" s="55" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B7" s="56" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C7" s="57"/>
       <x:c r="D7" s="57"/>
       <x:c r="E7" s="58"/>
       <x:c r="F7" s="58"/>
       <x:c r="G7" s="57" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H7" s="57" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="I7" s="57"/>
       <x:c r="J7" s="59"/>
@@ -1937,7 +1962,7 @@
       <x:c r="Q7" s="57"/>
       <x:c r="R7" s="60"/>
       <x:c r="S7" s="57" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="T7" s="61"/>
       <x:c r="U7" s="61"/>
@@ -1950,18 +1975,18 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="W8" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:23" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
       <x:c r="B9" s="2" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C9" s="2" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D9" s="2" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E9" s="3">
         <x:v>1</x:v>
@@ -1970,28 +1995,28 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G9" s="39" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="H9" s="37" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="I9" s="2" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="J9" s="4" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="K9" s="4">
         <x:v>397500</x:v>
       </x:c>
       <x:c r="L9" s="4" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="M9" s="2" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="N9" s="2" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="O9" s="40" t="s">
         <x:v>75</x:v>
@@ -2000,30 +2025,30 @@
         <x:v>46213.3979166667</x:v>
       </x:c>
       <x:c r="Q9" s="2" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="S9" s="2" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="T9" s="62" t="s">
-        <x:v>148</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="U9" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="W9" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:23" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <x:c r="B10" s="2" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C10" s="2" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D10" s="2" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E10" s="3">
         <x:v>1</x:v>
@@ -2032,60 +2057,60 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G10" s="39" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="H10" s="37" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="I10" s="2" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="J10" s="4" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="K10" s="4">
         <x:v>308500</x:v>
       </x:c>
       <x:c r="L10" s="4" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="M10" s="2" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="N10" s="2" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="O10" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="P10" s="5">
         <x:v>46213.5347222222</x:v>
       </x:c>
       <x:c r="Q10" s="2" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="S10" s="37" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="T10" s="62" t="s">
-        <x:v>148</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="U10" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="W10" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:23" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <x:c r="B11" s="2" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C11" s="2" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D11" s="2" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E11" s="3">
         <x:v>1</x:v>
@@ -2094,64 +2119,64 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G11" s="38" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H11" s="37" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="I11" s="2" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="J11" s="4" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="K11" s="4">
         <x:v>220000</x:v>
       </x:c>
       <x:c r="L11" s="4" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="M11" s="2" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="N11" s="2" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="O11" s="2" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="P11" s="5">
         <x:v>46213.6298611111</x:v>
       </x:c>
       <x:c r="Q11" s="2" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="S11" s="37" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="T11" s="62" t="s">
-        <x:v>148</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="U11" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="W11" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:23" x14ac:dyDescent="0.35">
       <x:c r="W12" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:23" x14ac:dyDescent="0.35">
       <x:c r="W13" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:23" x14ac:dyDescent="0.35">
       <x:c r="W14" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2198,8 +2223,8 @@
     <x:col min="2" max="2" width="24.726562" style="2" customWidth="1"/>
     <x:col min="3" max="3" width="18.726562" style="2" customWidth="1"/>
     <x:col min="4" max="4" width="14.726562" style="1" customWidth="1"/>
-    <x:col min="5" max="5" width="50.726562" style="2" customWidth="1"/>
-    <x:col min="6" max="6" width="16.726562" style="2" customWidth="1"/>
+    <x:col min="5" max="5" width="18.710625" style="2" customWidth="1"/>
+    <x:col min="6" max="6" width="24.710625" style="2" customWidth="1"/>
     <x:col min="7" max="8" width="14.726562" style="1" customWidth="1"/>
     <x:col min="9" max="12" width="28.726562" style="4" customWidth="1"/>
     <x:col min="13" max="13" width="22.726562" style="5" customWidth="1"/>
@@ -2211,21 +2236,25 @@
     <x:col min="19" max="16384" width="9.179688" style="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <x:row r="1" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <x:c r="A1" s="41" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="42" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C1" s="43" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D1" s="63" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="E1" s="11"/>
-      <x:c r="F1" s="11"/>
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E1" s="43" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="F1" s="42" t="s">
+        <x:v>151</x:v>
+      </x:c>
       <x:c r="I1" s="12"/>
       <x:c r="J1" s="12"/>
       <x:c r="K1" s="12"/>
@@ -2235,12 +2264,12 @@
       <x:c r="O1" s="13"/>
       <x:c r="P1" s="11"/>
     </x:row>
-    <x:row r="2" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <x:row r="2" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <x:c r="A2" s="41" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B2" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C2" s="11"/>
       <x:c r="E2" s="11"/>
@@ -2254,276 +2283,276 @@
       <x:c r="O2" s="13"/>
       <x:c r="P2" s="11"/>
     </x:row>
-    <x:row r="3" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <x:row r="3" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <x:c r="A3" s="44" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B3" s="45" t="s">
-        <x:v>94</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C3" s="46" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D3" s="64" t="s">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E3" s="46" t="s">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F3" s="46" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="G3" s="64" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H3" s="64" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="I3" s="48" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="J3" s="48" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="K3" s="48" t="s">
-        <x:v>102</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="L3" s="48" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="M3" s="49" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="N3" s="46" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="O3" s="49" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="P3" s="46" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="Q3" s="50" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="R3" s="50" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.35">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <x:c r="A4" s="44" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B4" s="45" t="s">
-        <x:v>104</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C4" s="46" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D4" s="54" t="s">
-        <x:v>105</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E4" s="46" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F4" s="46" t="s">
-        <x:v>107</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="G4" s="54" t="s">
-        <x:v>108</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="H4" s="54" t="s">
-        <x:v>109</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="I4" s="52" t="s">
-        <x:v>110</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="J4" s="52" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="K4" s="52" t="s">
-        <x:v>112</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="L4" s="52" t="s">
-        <x:v>113</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="M4" s="53" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="N4" s="46" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="O4" s="53" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="P4" s="46" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Q4" s="54"/>
       <x:c r="R4" s="54"/>
     </x:row>
-    <x:row r="5" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <x:row r="5" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <x:c r="A5" s="44" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B5" s="45" t="s">
-        <x:v>114</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C5" s="46" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D5" s="64" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E5" s="46" t="s">
-        <x:v>116</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="F5" s="46" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G5" s="64" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="H5" s="64" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="I5" s="48" t="s">
-        <x:v>117</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="J5" s="48" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K5" s="48" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L5" s="48" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="M5" s="49" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="N5" s="46" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="O5" s="49" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="O5" s="49" t="s">
-        <x:v>54</x:v>
-      </x:c>
       <x:c r="P5" s="46" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Q5" s="54"/>
       <x:c r="R5" s="54"/>
     </x:row>
-    <x:row r="6" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <x:row r="6" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <x:c r="A6" s="41" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B6" s="45" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C6" s="46" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D6" s="64" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E6" s="46" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F6" s="46" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G6" s="64" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H6" s="64" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="I6" s="48" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="J6" s="48" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="K6" s="48" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="L6" s="48" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M6" s="49" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="N6" s="46" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="H6" s="64" t="s">
+      <x:c r="O6" s="49" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="P6" s="46" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="I6" s="48" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="J6" s="48" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="K6" s="48" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="L6" s="48" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="M6" s="49" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="N6" s="46" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="O6" s="49" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="P6" s="46" t="s">
-        <x:v>58</x:v>
       </x:c>
       <x:c r="Q6" s="54"/>
       <x:c r="R6" s="54"/>
     </x:row>
-    <x:row r="7" spans="1:19" x14ac:dyDescent="0.35">
+    <x:row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <x:c r="A7" s="55" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B7" s="56" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C7" s="57" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D7" s="65" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E7" s="57" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F7" s="57" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G7" s="65" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H7" s="65" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="I7" s="59" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J7" s="59" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K7" s="59" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L7" s="59" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M7" s="60" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="N7" s="57" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="O7" s="60" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="P7" s="57" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Q7" s="61"/>
       <x:c r="R7" s="61"/>
     </x:row>
-    <x:row r="8" spans="1:19" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <x:row r="8" spans="1:18" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <x:c r="A8" s="1" t="s">
         <x:v>64</x:v>
       </x:c>
       <x:c r="C8" s="2" t="s">
-        <x:v>119</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2569,8 +2598,10 @@
     <x:col min="1" max="1" width="16.269531" style="1" customWidth="1"/>
     <x:col min="2" max="2" width="24.726562" style="2" customWidth="1"/>
     <x:col min="3" max="3" width="18.726562" style="2" customWidth="1"/>
-    <x:col min="4" max="5" width="16.726562" style="2" customWidth="1"/>
-    <x:col min="6" max="7" width="14.726562" style="3" customWidth="1"/>
+    <x:col min="4" max="4" width="16.726562" style="2" customWidth="1"/>
+    <x:col min="5" max="5" width="18.710625" style="2" customWidth="1"/>
+    <x:col min="6" max="6" width="24.710625" style="3" customWidth="1"/>
+    <x:col min="7" max="7" width="14.726562" style="3" customWidth="1"/>
     <x:col min="8" max="8" width="39.269531" style="2" customWidth="1"/>
     <x:col min="9" max="10" width="16.726562" style="2" customWidth="1"/>
     <x:col min="11" max="13" width="28.726562" style="4" customWidth="1"/>
@@ -2590,16 +2621,20 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="42" t="s">
-        <x:v>118</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C1" s="43" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D1" s="42" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="E1" s="11"/>
-      <x:c r="F1" s="10"/>
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="E1" s="43" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="F1" s="67" t="s">
+        <x:v>151</x:v>
+      </x:c>
       <x:c r="G1" s="10"/>
       <x:c r="H1" s="11"/>
       <x:c r="I1" s="11"/>
@@ -2620,7 +2655,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B2" s="36" t="s">
-        <x:v>149</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C2" s="11"/>
       <x:c r="D2" s="11"/>
@@ -2643,270 +2678,270 @@
     </x:row>
     <x:row r="3" spans="1:24" ht="29" customHeight="1" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <x:c r="A3" s="44" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B3" s="45" t="s">
-        <x:v>121</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C3" s="46" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D3" s="46" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E3" s="46" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F3" s="47" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G3" s="47" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H3" s="46" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="I3" s="46" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="J3" s="46" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K3" s="48" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="L3" s="48" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="M3" s="48" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N3" s="46" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="O3" s="46" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="P3" s="46" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Q3" s="49" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="R3" s="46" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="S3" s="49" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="T3" s="46" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="U3" s="50" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="V3" s="50" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:24" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <x:c r="A4" s="44" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B4" s="45" t="s">
-        <x:v>122</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C4" s="46" t="s">
-        <x:v>123</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D4" s="46" t="s">
-        <x:v>124</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="E4" s="46" t="s">
-        <x:v>125</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="F4" s="51" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G4" s="51" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H4" s="46" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="I4" s="46" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="J4" s="46" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="K4" s="52" t="s">
-        <x:v>126</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="L4" s="52" t="s">
-        <x:v>127</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="M4" s="52" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="N4" s="46" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="O4" s="46" t="s">
-        <x:v>128</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="P4" s="46" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="Q4" s="53" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="R4" s="46" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="S4" s="53" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="T4" s="46" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="U4" s="54"/>
       <x:c r="V4" s="54"/>
     </x:row>
     <x:row r="5" spans="1:24" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <x:c r="A5" s="44" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B5" s="45" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C5" s="46" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D5" s="46" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E5" s="46" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F5" s="47" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G5" s="47" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="H5" s="46" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I5" s="46" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="J5" s="46" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="K5" s="48" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="L5" s="48" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="M5" s="48" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="N5" s="46" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="G5" s="47" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="H5" s="46" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="I5" s="46" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="J5" s="46" t="s">
+      <x:c r="O5" s="46" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="K5" s="48" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="L5" s="48" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="M5" s="48" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="N5" s="46" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="O5" s="46" t="s">
-        <x:v>50</x:v>
-      </x:c>
       <x:c r="P5" s="46" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Q5" s="49" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="R5" s="46" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="S5" s="49" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="S5" s="49" t="s">
-        <x:v>54</x:v>
-      </x:c>
       <x:c r="T5" s="46" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="U5" s="54"/>
       <x:c r="V5" s="54"/>
     </x:row>
     <x:row r="6" spans="1:24" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <x:c r="A6" s="41" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B6" s="45" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C6" s="46" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D6" s="46" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E6" s="46" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F6" s="47" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G6" s="47" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H6" s="46" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="I6" s="46" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="J6" s="46" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="K6" s="48" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="L6" s="48" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M6" s="48" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="N6" s="46" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="I6" s="46" t="s">
+      <x:c r="O6" s="46" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="P6" s="46" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="J6" s="46" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="K6" s="48" t="s">
+      <x:c r="Q6" s="49" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="R6" s="46" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="L6" s="48" t="s">
+      <x:c r="S6" s="49" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="T6" s="46" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="M6" s="48" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N6" s="46" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="O6" s="46" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="P6" s="46" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="Q6" s="49" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="R6" s="46" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="S6" s="49" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="T6" s="46" t="s">
-        <x:v>58</x:v>
       </x:c>
       <x:c r="U6" s="54"/>
       <x:c r="V6" s="54"/>
     </x:row>
     <x:row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <x:c r="A7" s="55" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B7" s="56" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C7" s="57"/>
       <x:c r="D7" s="57"/>
@@ -2914,10 +2949,10 @@
       <x:c r="F7" s="58"/>
       <x:c r="G7" s="58"/>
       <x:c r="H7" s="57" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="I7" s="57" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J7" s="57"/>
       <x:c r="K7" s="59"/>
@@ -2930,7 +2965,7 @@
       <x:c r="R7" s="57"/>
       <x:c r="S7" s="60"/>
       <x:c r="T7" s="57" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="U7" s="61"/>
       <x:c r="V7" s="61"/>
@@ -2940,24 +2975,24 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="C8" s="2" t="s">
-        <x:v>129</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="X8" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:24" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <x:c r="B9" s="2" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C9" s="2" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D9" s="2" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E9" s="2" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F9" s="3">
         <x:v>1</x:v>
@@ -2966,63 +3001,63 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H9" s="39" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="I9" s="37" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J9" s="2" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="K9" s="4" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="L9" s="4">
         <x:v>397500</x:v>
       </x:c>
       <x:c r="M9" s="4" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="N9" s="2" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="O9" s="2" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="P9" s="2" t="s">
-        <x:v>131</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="Q9" s="5">
         <x:v>46223.3979166667</x:v>
       </x:c>
       <x:c r="R9" s="2" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="T9" s="2" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="U9" s="62" t="s">
-        <x:v>148</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="V9" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="X9" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>134</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:24" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <x:c r="B10" s="2" t="s">
-        <x:v>133</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C10" s="2" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D10" s="2" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E10" s="2" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F10" s="3">
         <x:v>1</x:v>
@@ -3031,63 +3066,63 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H10" s="39" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="I10" s="37" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J10" s="2" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="K10" s="4" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="L10" s="4">
         <x:v>308500</x:v>
       </x:c>
       <x:c r="M10" s="4" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="N10" s="2" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="O10" s="2" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="P10" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q10" s="5">
         <x:v>46223.5347222222</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="T10" s="37" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="U10" s="62" t="s">
-        <x:v>148</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="V10" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="X10" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:24" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <x:c r="B11" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C11" s="2" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D11" s="2" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E11" s="2" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F11" s="3">
         <x:v>1</x:v>
@@ -3096,64 +3131,64 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H11" s="38" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="I11" s="37" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="J11" s="2" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="K11" s="4" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="L11" s="4">
         <x:v>220000</x:v>
       </x:c>
       <x:c r="M11" s="4" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="N11" s="2" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="O11" s="2" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="P11" s="2" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="Q11" s="5">
         <x:v>46223.6298611111</x:v>
       </x:c>
       <x:c r="R11" s="2" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="T11" s="37" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="U11" s="62" t="s">
-        <x:v>148</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="V11" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="X11" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:24" x14ac:dyDescent="0.35">
       <x:c r="X12" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:24" x14ac:dyDescent="0.35">
       <x:c r="X13" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:24" x14ac:dyDescent="0.35">
       <x:c r="X14" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3200,8 +3235,8 @@
     <x:col min="2" max="2" width="24.726562" style="2" customWidth="1"/>
     <x:col min="3" max="3" width="18.726562" style="2" customWidth="1"/>
     <x:col min="4" max="4" width="30.726562" style="2" customWidth="1"/>
-    <x:col min="5" max="5" width="14.726562" style="1" customWidth="1"/>
-    <x:col min="6" max="6" width="50.726562" style="2" customWidth="1"/>
+    <x:col min="5" max="5" width="18.710625" style="1" customWidth="1"/>
+    <x:col min="6" max="6" width="24.710625" style="2" customWidth="1"/>
     <x:col min="7" max="7" width="16.726562" style="2" customWidth="1"/>
     <x:col min="8" max="9" width="14.726562" style="1" customWidth="1"/>
     <x:col min="10" max="13" width="28.726562" style="4" customWidth="1"/>
@@ -3214,20 +3249,25 @@
     <x:col min="20" max="16384" width="9.179688" style="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <x:row r="1" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <x:c r="A1" s="41" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="42" t="s">
-        <x:v>139</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C1" s="43" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D1" s="42" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="F1" s="11"/>
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="E1" s="41" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="F1" s="42" t="s">
+        <x:v>151</x:v>
+      </x:c>
       <x:c r="G1" s="11"/>
       <x:c r="J1" s="12"/>
       <x:c r="K1" s="12"/>
@@ -3238,12 +3278,12 @@
       <x:c r="P1" s="13"/>
       <x:c r="Q1" s="11"/>
     </x:row>
-    <x:row r="2" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <x:row r="2" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <x:c r="A2" s="41" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B2" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C2" s="11"/>
       <x:c r="D2" s="11"/>
@@ -3258,286 +3298,286 @@
       <x:c r="P2" s="13"/>
       <x:c r="Q2" s="11"/>
     </x:row>
-    <x:row r="3" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <x:row r="3" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <x:c r="A3" s="44" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B3" s="45" t="s">
-        <x:v>94</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C3" s="46" t="s">
-        <x:v>121</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D3" s="46" t="s">
-        <x:v>141</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="E3" s="64" t="s">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F3" s="46" t="s">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="G3" s="46" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="H3" s="64" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="I3" s="64" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="J3" s="48" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="K3" s="48" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="L3" s="48" t="s">
-        <x:v>102</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="M3" s="48" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="N3" s="49" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="O3" s="46" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="P3" s="49" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="Q3" s="46" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="R3" s="50" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="S3" s="50" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.35">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <x:c r="A4" s="44" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B4" s="45" t="s">
-        <x:v>104</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C4" s="46" t="s">
-        <x:v>122</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D4" s="46" t="s">
-        <x:v>142</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="E4" s="54" t="s">
-        <x:v>105</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="F4" s="46" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="G4" s="46" t="s">
-        <x:v>107</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="H4" s="54" t="s">
-        <x:v>143</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="I4" s="54" t="s">
-        <x:v>144</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="J4" s="52" t="s">
-        <x:v>145</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="K4" s="52" t="s">
-        <x:v>146</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="L4" s="52" t="s">
-        <x:v>147</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="M4" s="52" t="s">
-        <x:v>113</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="N4" s="53" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="O4" s="46" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="P4" s="53" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="Q4" s="46" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="R4" s="54"/>
       <x:c r="S4" s="54"/>
     </x:row>
-    <x:row r="5" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <x:row r="5" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <x:c r="A5" s="44" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B5" s="45" t="s">
-        <x:v>114</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C5" s="46" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D5" s="46" t="s">
-        <x:v>114</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E5" s="64" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="F5" s="46" t="s">
-        <x:v>116</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="G5" s="46" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H5" s="64" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="I5" s="64" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="J5" s="48" t="s">
-        <x:v>117</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="K5" s="48" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L5" s="48" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="M5" s="48" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="N5" s="49" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="O5" s="46" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P5" s="49" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="P5" s="49" t="s">
-        <x:v>54</x:v>
-      </x:c>
       <x:c r="Q5" s="46" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="R5" s="54"/>
       <x:c r="S5" s="54"/>
     </x:row>
-    <x:row r="6" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <x:row r="6" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <x:c r="A6" s="41" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B6" s="45" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C6" s="46" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D6" s="46" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E6" s="64" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="E6" s="64" t="s">
-        <x:v>58</x:v>
-      </x:c>
       <x:c r="F6" s="46" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G6" s="46" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H6" s="64" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="I6" s="64" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="J6" s="48" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="K6" s="48" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="L6" s="48" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M6" s="48" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="N6" s="49" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="O6" s="46" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="I6" s="64" t="s">
+      <x:c r="P6" s="49" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="Q6" s="46" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="J6" s="48" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="K6" s="48" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="L6" s="48" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="M6" s="48" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N6" s="49" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="O6" s="46" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="P6" s="49" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="Q6" s="46" t="s">
-        <x:v>58</x:v>
       </x:c>
       <x:c r="R6" s="54"/>
       <x:c r="S6" s="54"/>
     </x:row>
-    <x:row r="7" spans="1:20" x14ac:dyDescent="0.35">
+    <x:row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <x:c r="A7" s="55" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B7" s="56" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C7" s="57" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D7" s="57" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E7" s="65" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F7" s="57" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G7" s="57" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H7" s="65" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="I7" s="65" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J7" s="59" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K7" s="59" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L7" s="59" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M7" s="59" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="N7" s="60" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="O7" s="57" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="P7" s="60" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Q7" s="57" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="R7" s="61"/>
       <x:c r="S7" s="61"/>
     </x:row>
-    <x:row r="8" spans="1:20">
+    <x:row r="8" spans="1:19">
       <x:c r="B8" s="2"/>
       <x:c r="C8" s="2"/>
       <x:c r="D8" s="2"/>
@@ -3552,7 +3592,7 @@
       <x:c r="P8" s="5"/>
       <x:c r="Q8" s="2"/>
     </x:row>
-    <x:row r="9" spans="1:20">
+    <x:row r="9" spans="1:19">
       <x:c r="B9" s="2"/>
       <x:c r="C9" s="2"/>
       <x:c r="D9" s="2"/>
@@ -3567,7 +3607,7 @@
       <x:c r="P9" s="5"/>
       <x:c r="Q9" s="2"/>
     </x:row>
-    <x:row r="10" spans="1:20">
+    <x:row r="10" spans="1:19">
       <x:c r="B10" s="2"/>
       <x:c r="C10" s="2"/>
       <x:c r="D10" s="2"/>
